--- a/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1.717658977987759</v>
+        <v>1.381477694510773</v>
       </c>
       <c r="B2">
-        <v>2.781512639797264</v>
+        <v>1.825780762238352</v>
       </c>
       <c r="C2">
-        <v>3.753440207905138</v>
+        <v>2.227938646094956</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1.381477694510773</v>
+        <v>6.029012150736055</v>
       </c>
       <c r="B2">
-        <v>1.825780762238352</v>
+        <v>7.914026027126907</v>
       </c>
       <c r="C2">
-        <v>2.227938646094956</v>
+        <v>9.6203140687185</v>
       </c>
       <c r="D2">
         <v>1</v>

--- a/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
+++ b/output/Tables/2019/Resampling/1km_soc_value_1000replicate.xlsx
@@ -378,13 +378,13 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>6.029012150736055</v>
+        <v>5.974699983458555</v>
       </c>
       <c r="B2">
-        <v>7.914026027126907</v>
+        <v>7.914210430492371</v>
       </c>
       <c r="C2">
-        <v>9.6203140687185</v>
+        <v>9.66971823652562</v>
       </c>
       <c r="D2">
         <v>1</v>
